--- a/Data/EXCEL/Transfer/salemon/202208/8467-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/8467-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76D4D709-64A6-416E-8C42-6547A1894574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7A0DD48-A379-467A-A261-01F456703177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="8467-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,17 +1227,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q86"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="5" width="9.625" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="10.5" customWidth="1"/>
-    <col min="8" max="16" width="9.625" customWidth="1"/>
-    <col min="17" max="17" width="10" customWidth="1"/>
+    <col min="1" max="1" width="16.75" customWidth="1"/>
+    <col min="2" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="13.375" customWidth="1"/>
+    <col min="7" max="7" width="15.375" customWidth="1"/>
+    <col min="8" max="16" width="14.125" customWidth="1"/>
+    <col min="17" max="17" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1256,7 +1264,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1295,7 +1303,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1338,7 +1346,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1377,7 +1385,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1430,7 +1438,7 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1483,7 +1491,7 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1536,7 +1544,7 @@
         <v>66.3</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1589,7 +1597,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1642,7 +1650,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1695,7 +1703,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1748,7 +1756,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1801,7 +1809,7 @@
         <v>222.6</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1854,7 +1862,7 @@
         <v>36.200000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1907,7 +1915,7 @@
         <v>37.799999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1960,7 +1968,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2013,7 +2021,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2066,7 +2074,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2119,7 +2127,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2172,7 +2180,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2225,7 +2233,7 @@
         <v>8.49</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2278,7 +2286,7 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2331,7 +2339,7 @@
         <v>38.799999999999997</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2384,7 +2392,7 @@
         <v>42.8</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2437,7 +2445,7 @@
         <v>-35.1</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2490,7 +2498,7 @@
         <v>-28</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2543,7 +2551,7 @@
         <v>-28.6</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2596,7 +2604,7 @@
         <v>-27.5</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2649,7 +2657,7 @@
         <v>-25.9</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2702,7 +2710,7 @@
         <v>-24</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2755,7 +2763,7 @@
         <v>-21.9</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2808,7 +2816,7 @@
         <v>-26.6</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2861,7 +2869,7 @@
         <v>-15.4</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2914,7 +2922,7 @@
         <v>-31.9</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2967,7 +2975,7 @@
         <v>-24</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3020,7 +3028,7 @@
         <v>-20.2</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3073,7 +3081,7 @@
         <v>-2.75</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3126,7 +3134,7 @@
         <v>-3.23</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3179,7 +3187,7 @@
         <v>-5.53</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3232,7 +3240,7 @@
         <v>-5.48</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3285,7 +3293,7 @@
         <v>-7.08</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3338,7 +3346,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3391,7 +3399,7 @@
         <v>-9.02</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3444,7 +3452,7 @@
         <v>-2.17</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3497,7 +3505,7 @@
         <v>-10.6</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3550,7 +3558,7 @@
         <v>-3.01</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3603,7 +3611,7 @@
         <v>-15.8</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3656,7 +3664,7 @@
         <v>-30.7</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3709,7 +3717,7 @@
         <v>-39.299999999999997</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3762,7 +3770,7 @@
         <v>-5.03</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3815,7 +3823,7 @@
         <v>-1.49</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3868,7 +3876,7 @@
         <v>-0.26</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3921,7 +3929,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3974,7 +3982,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4027,7 +4035,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4080,7 +4088,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4133,7 +4141,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4186,7 +4194,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43160</v>
       </c>
@@ -4239,7 +4247,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43132</v>
       </c>
@@ -4292,7 +4300,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43101</v>
       </c>
@@ -4345,7 +4353,7 @@
         <v>93.7</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43070</v>
       </c>
@@ -4398,7 +4406,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43040</v>
       </c>
@@ -4451,7 +4459,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>43009</v>
       </c>
@@ -4504,7 +4512,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42979</v>
       </c>
@@ -4557,7 +4565,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42948</v>
       </c>
@@ -4610,7 +4618,7 @@
         <v>6.15</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42917</v>
       </c>
@@ -4663,7 +4671,7 @@
         <v>-1.35</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42887</v>
       </c>
@@ -4716,7 +4724,7 @@
         <v>-11.3</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42856</v>
       </c>
@@ -4769,7 +4777,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42826</v>
       </c>
@@ -4822,7 +4830,7 @@
         <v>-23.1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42795</v>
       </c>
@@ -4875,7 +4883,7 @@
         <v>-12.5</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42767</v>
       </c>
@@ -4928,7 +4936,7 @@
         <v>-14.3</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42736</v>
       </c>
@@ -4981,7 +4989,7 @@
         <v>-22.4</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42705</v>
       </c>
@@ -5034,7 +5042,7 @@
         <v>-23.4</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42675</v>
       </c>
@@ -5087,7 +5095,7 @@
         <v>-22.6</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42644</v>
       </c>
@@ -5140,7 +5148,7 @@
         <v>-18.3</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42614</v>
       </c>
@@ -5193,7 +5201,7 @@
         <v>-20.9</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42583</v>
       </c>
@@ -5246,7 +5254,7 @@
         <v>-26.8</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42552</v>
       </c>
@@ -5299,7 +5307,7 @@
         <v>-29.7</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42522</v>
       </c>
@@ -5352,7 +5360,7 @@
         <v>-26.7</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42491</v>
       </c>
@@ -5405,7 +5413,7 @@
         <v>-19.3</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42461</v>
       </c>
@@ -5458,7 +5466,7 @@
         <v>-21.1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42430</v>
       </c>
@@ -5511,7 +5519,7 @@
         <v>-21.8</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42401</v>
       </c>
@@ -5564,7 +5572,7 @@
         <v>-4.4400000000000004</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42370</v>
       </c>
@@ -5617,7 +5625,7 @@
         <v>-22.9</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42339</v>
       </c>
@@ -5670,7 +5678,7 @@
         <v>-14.6</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="5" customFormat="1">
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>42309</v>
       </c>
@@ -5738,7 +5746,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>